--- a/J30/Output_files/Tran_log_Detail_Results.xlsx
+++ b/J30/Output_files/Tran_log_Detail_Results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,32 +488,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7679833253678907188</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>0215055283</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>3503907110</t>
-        </is>
-      </c>
+          <t>7683588273628895195</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>706510-306-L/XL</t>
+          <t>136064-006-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20251204155507000004</t>
+          <t>20260114000000000001</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -528,72 +520,456 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CG</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AVAILABLE</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>kson15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7679844135999185842</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0215055283</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>3503907110</t>
-        </is>
-      </c>
+          <t>7683588537428974916</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>706510-306-L/XL</t>
+          <t>136064-006-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20251204155507000004</t>
+          <t>20260114000000000002</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AVAILABLE</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>AVAILABLE</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>kson15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>7683596685089223001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>136064-006-10</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>20260114000000000002</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>CG</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AVAILABLE</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>AVAILABLE</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>kson15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>7683596685479276001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>136064-006-10</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>20260114000000000001</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>AVAILABLE</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>kson15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7683747235354078221</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>136064-006-10</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>20260114000000000001</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>AVAILABLE</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>kson15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>7683747462004151007</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>136064-006-10</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20260114000000000002</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>AVAILABLE</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>kson15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7684524760653409190</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>136064-006-10</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>20260114000000000001</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>AVAILABLE</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7684524946473481209</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>136064-006-10</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>20260114000000000002</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>AVAILABLE</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7684534920604296435</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>136064-006-10</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>20260114000000000002</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>AVAILABLE</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vgana3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>7684534921024344067</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>136064-006-10</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>20260114000000000001</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>AVAILABLE</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>vgana3</t>
         </is>
